--- a/Deepak R/PlaywrightAutomation/test-data/Excel_test_data.xlsx
+++ b/Deepak R/PlaywrightAutomation/test-data/Excel_test_data.xlsx
@@ -110,16 +110,16 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>"password"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>:</t>
+      <t>"shopping items"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>: [</t>
     </r>
     <r>
       <rPr>
@@ -128,7 +128,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>"secret_sauce"</t>
+      <t>"Sauce Labs Backpack"</t>
     </r>
     <r>
       <rPr>
@@ -138,6 +138,42 @@
         <family val="3"/>
       </rPr>
       <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Sauce Labs Bolt T-Shirt"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCE9178"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>"Sauce Labs Onesie"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>]</t>
     </r>
   </si>
   <si>
@@ -151,16 +187,16 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>"shopping items"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>: [</t>
+      <t>"password"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFCCCCCC"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>:</t>
     </r>
     <r>
       <rPr>
@@ -169,7 +205,7 @@
         <rFont val="Consolas"/>
         <family val="3"/>
       </rPr>
-      <t>"Sauce Labs Backpack"</t>
+      <t>"  secret_sauce"</t>
     </r>
     <r>
       <rPr>
@@ -179,42 +215,6 @@
         <family val="3"/>
       </rPr>
       <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCE9178"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>"Sauce Labs Bolt T-Shirt"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCE9178"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>"Sauce Labs Onesie"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFCCCCCC"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>]</t>
     </r>
   </si>
 </sst>
@@ -577,6 +577,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.85546875" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -590,12 +594,12 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
